--- a/output/pdf_financials_xlsx/NBLC.xlsx
+++ b/output/pdf_financials_xlsx/NBLC.xlsx
@@ -3950,19 +3950,19 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.954285</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.953968</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.557256</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.376987</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.048583</v>
       </c>
     </row>
     <row r="93">
@@ -6118,7 +6118,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -6498,7 +6502,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -7372,7 +7380,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NBLC.xlsx
+++ b/output/pdf_financials_xlsx/NBLC.xlsx
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.01347</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1457,7 +1457,7 @@
         <v>-3.349814</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.836074</v>
+        <v>-0.849544</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.781461</v>
@@ -1531,7 +1531,7 @@
         <v>-3.349814</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.836074</v>
+        <v>-0.849544</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.781461</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.003695</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.006243</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>4.075028</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.841075</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.415026</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.36481</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.712152</v>
       </c>
     </row>
     <row r="35">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.01</v>
+        <v>0.013695</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.01</v>
@@ -1791,22 +1791,22 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.006243</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>4.075028</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.841075</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.415026</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.36481</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.712152</v>
       </c>
     </row>
     <row r="37">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.004411</v>
+        <v>0.0007159999999999999</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.002637</v>
@@ -2235,13 +2235,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.006243</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.139634</v>
+        <v>0.064606</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.852232</v>
+        <v>0.011157</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -18656,7 +18656,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">

--- a/output/pdf_financials_xlsx/NBLC.xlsx
+++ b/output/pdf_financials_xlsx/NBLC.xlsx
@@ -649,19 +649,19 @@
         <v>0.02004</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.497851</v>
+        <v>1.642281</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.8732220000000001</v>
+        <v>0.935662</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.027018</v>
+        <v>1.085459</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.070414</v>
+        <v>1.125258</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.751023</v>
+        <v>0.809962</v>
       </c>
     </row>
     <row r="8">
@@ -760,19 +760,19 @@
         <v>0.02004</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.497851</v>
+        <v>1.642281</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.8732220000000001</v>
+        <v>0.935662</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.027018</v>
+        <v>1.085459</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.070414</v>
+        <v>1.125258</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.751023</v>
+        <v>0.809962</v>
       </c>
     </row>
     <row r="11">
@@ -797,19 +797,19 @@
         <v>-0.02004</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-1.497851</v>
+        <v>-1.642281</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.8732220000000001</v>
+        <v>-0.935662</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.027018</v>
+        <v>-1.085459</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1.070414</v>
+        <v>-1.125258</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.751023</v>
+        <v>-0.809962</v>
       </c>
     </row>
     <row r="12">
@@ -2876,13 +2876,13 @@
         <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.297469</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.228871</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.339322</v>
       </c>
     </row>
     <row r="65">
@@ -2987,13 +2987,13 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.651667</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.396491</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.238563</v>
       </c>
     </row>
     <row r="68">
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003686</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0</v>
@@ -10776,7 +10776,11 @@
           <t>Payment of share issuance costs related to private placement 6</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -12356,7 +12360,11 @@
           <t>Payment of share issuance costs related to private placement 7</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -13216,7 +13224,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -14098,7 +14110,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -16856,7 +16872,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
